--- a/jpcore-r4b/develop/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-researchsubject.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-researchsubject.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="246">
   <si>
     <t>Property</t>
   </si>
@@ -266,17 +266,17 @@
 </t>
   </si>
   <si>
-    <t>Physical entity which is the primary unit of interest in the study</t>
-  </si>
-  <si>
-    <t>A physical entity which is the primary unit of operational and/or administrative interest in a study.</t>
-  </si>
-  <si>
-    <t>Need to make sure we encompass public health studies.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>研究に関心のある主要な単位である物理的実体 / Physical entity which is the primary unit of interest in the study</t>
+  </si>
+  <si>
+    <t>研究における運用上および/または管理上の関心の主要な単位である物理的エンティティ。 / A physical entity which is the primary unit of operational and/or administrative interest in a study.</t>
+  </si>
+  <si>
+    <t>公衆衛生研究を網羅することを確認する必要があります。 / Need to make sure we encompass public health studies.</t>
+  </si>
+  <si>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>StudySubject</t>
@@ -304,13 +304,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -323,26 +323,26 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>ResearchSubject.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -362,13 +362,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -384,23 +384,27 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchSubject.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>ResearchSubject.meta.lastUpdated</t>
@@ -410,13 +414,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -429,13 +433,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -449,13 +454,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -468,13 +473,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -489,13 +494,13 @@
     <t>ResearchSubject.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -510,13 +515,13 @@
     <t>ResearchSubject.implicitRules</t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -529,19 +534,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -561,13 +566,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -587,19 +592,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -609,23 +614,34 @@
     <t>ResearchSubject.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>ResearchSubject.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -638,10 +654,10 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for research subject in a study</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this research subject for a study.</t>
+    <t>研究の研究対象のビジネスidentifier / Business Identifier for research subject in a study</t>
+  </si>
+  <si>
+    <t>研究のためにこの研究対象に割り当てられたidentifier。 / Identifiers assigned to this research subject for a study.</t>
   </si>
   <si>
     <t>StudySubject &gt; Subject.identifier</t>
@@ -656,16 +672,16 @@
     <t>ResearchSubject.status</t>
   </si>
   <si>
-    <t>candidate | eligible | follow-up | ineligible | not-registered | off-study | on-study | on-study-intervention | on-study-observation | pending-on-study | potential-candidate | screening | withdrawn</t>
-  </si>
-  <si>
-    <t>The current state of the subject.</t>
+    <t>候補者|対象|フォローアップ|不適格|登録なし|オフスタディ|on-study |instudy-intervention |on-study-observation |保留中のスタディ|潜在的なキャンディデート|スクリーニング|引きこもった / candidate | eligible | follow-up | ineligible | not-registered | off-study | on-study | on-study-intervention | on-study-observation | pending-on-study | potential-candidate | screening | withdrawn</t>
+  </si>
+  <si>
+    <t>主題の現状。 / The current state of the subject.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Indicates the progression of a study subject through a study.</t>
+    <t>研究を通じて研究対象の進行を示します。 / Indicates the progression of a study subject through a study.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/research-subject-status|4.3.0</t>
@@ -691,10 +707,10 @@
 </t>
   </si>
   <si>
-    <t>Start and end of participation</t>
-  </si>
-  <si>
-    <t>The dates the subject began and ended their participation in the study.</t>
+    <t>参加の開始と終了 / Start and end of participation</t>
+  </si>
+  <si>
+    <t>被験者の日付は始まり、研究への参加を終了しました。 / The dates the subject began and ended their participation in the study.</t>
   </si>
   <si>
     <t>PerformedStudySubjectMilestone.studyReferenceDateRange</t>
@@ -710,10 +726,10 @@
 </t>
   </si>
   <si>
-    <t>Study subject is part of</t>
-  </si>
-  <si>
-    <t>Reference to the study the subject is participating in.</t>
+    <t>研究対象はの一部です / Study subject is part of</t>
+  </si>
+  <si>
+    <t>被験者が参加している研究への参照。 / Reference to the study the subject is participating in.</t>
   </si>
   <si>
     <t>StudySubjectProtocolVersionRelationship</t>
@@ -726,10 +742,10 @@
 </t>
   </si>
   <si>
-    <t>Who is part of study</t>
-  </si>
-  <si>
-    <t>The record of the person or animal who is involved in the study.</t>
+    <t>勉強の一部です / Who is part of study</t>
+  </si>
+  <si>
+    <t>研究に関与している人または動物の記録。 / The record of the person or animal who is involved in the study.</t>
   </si>
   <si>
     <t>ResearchSubject.assignedArm</t>
@@ -739,10 +755,10 @@
 </t>
   </si>
   <si>
-    <t>What path should be followed</t>
-  </si>
-  <si>
-    <t>The name of the arm in the study the subject is expected to follow as part of this study.</t>
+    <t>どの道をたどるべきか / What path should be followed</t>
+  </si>
+  <si>
+    <t>この研究の腕の名前は、この研究の一部として続くと予想されます。 / The name of the arm in the study the subject is expected to follow as part of this study.</t>
   </si>
   <si>
     <t>Arm &gt; ExperimentalUnit &gt; BiologicEntity &gt; Subject &gt; StudySubject</t>
@@ -751,10 +767,10 @@
     <t>ResearchSubject.actualArm</t>
   </si>
   <si>
-    <t>What path was followed</t>
-  </si>
-  <si>
-    <t>The name of the arm in the study the subject actually followed as part of this study.</t>
+    <t>どの道が続きましたか / What path was followed</t>
+  </si>
+  <si>
+    <t>この研究の腕の名前は、この研究の一環として実際に続きました。 / The name of the arm in the study the subject actually followed as part of this study.</t>
   </si>
   <si>
     <t>ResearchSubject.consent</t>
@@ -764,10 +780,10 @@
 </t>
   </si>
   <si>
-    <t>Agreement to participate in study</t>
-  </si>
-  <si>
-    <t>A record of the patient's informed agreement to participate in the study.</t>
+    <t>研究に参加するための合意 / Agreement to participate in study</t>
+  </si>
+  <si>
+    <t>研究に参加するための患者の情報に基づいた合意の記録。 / A record of the patient's informed agreement to participate in the study.</t>
   </si>
   <si>
     <t>ResearchStudy.consent is related to PerformedStudySubjectMilestone.informedConsentIndicator in that the informedConsentIndicator can be derived from the data in the Consent resource.</t>
@@ -1114,7 +1130,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="48.91015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.359375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="45.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1918,7 +1934,7 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
@@ -1935,10 +1951,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1961,16 +1977,16 @@
         <v>92</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2020,7 +2036,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2032,7 +2048,7 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -2049,10 +2065,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2075,16 +2091,16 @@
         <v>92</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2134,7 +2150,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2146,7 +2162,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2163,10 +2179,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2189,16 +2205,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2248,7 +2264,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2260,7 +2276,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2277,10 +2293,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2303,16 +2319,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2338,11 +2354,11 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -2360,7 +2376,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2372,7 +2388,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -2389,10 +2405,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2415,16 +2431,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2450,11 +2466,11 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -2472,7 +2488,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2484,7 +2500,7 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -2501,10 +2517,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2527,16 +2543,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2586,7 +2602,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2615,10 +2631,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2641,16 +2657,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2676,13 +2692,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -2700,7 +2716,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2729,14 +2745,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2755,16 +2771,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2814,7 +2830,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2835,7 +2851,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -2843,14 +2859,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2869,16 +2885,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2928,7 +2944,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2940,7 +2956,7 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -2949,7 +2965,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -2957,10 +2973,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2986,13 +3002,13 @@
         <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3042,7 +3058,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3054,7 +3070,7 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>119</v>
+        <v>195</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -3063,7 +3079,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -3071,10 +3087,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3100,16 +3116,16 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3158,7 +3174,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3170,7 +3186,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>119</v>
+        <v>195</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -3179,7 +3195,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -3187,10 +3203,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3213,13 +3229,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3270,7 +3286,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3285,24 +3301,24 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3325,13 +3341,13 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3358,31 +3374,31 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -3397,28 +3413,28 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3437,13 +3453,13 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3494,7 +3510,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3509,7 +3525,7 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
@@ -3518,15 +3534,15 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3549,13 +3565,13 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3606,7 +3622,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>91</v>
@@ -3621,7 +3637,7 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
@@ -3635,10 +3651,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3661,13 +3677,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3718,7 +3734,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>91</v>
@@ -3747,10 +3763,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3773,13 +3789,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3830,7 +3846,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3845,7 +3861,7 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -3859,10 +3875,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3885,13 +3901,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3942,7 +3958,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3957,7 +3973,7 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -3971,10 +3987,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3997,13 +4013,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4054,7 +4070,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4069,7 +4085,7 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>80</v>
